--- a/resources/Part_3_Statistics/S21_L136/4.10.Hypothesis-testing-section-practical-example-exercise.xlsx
+++ b/resources/Part_3_Statistics/S21_L136/4.10.Hypothesis-testing-section-practical-example-exercise.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="18625"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Iliya\Desktop\Statistics for Data Science and Business Analysis\Filming\Final excel\Section 4 - Hypothesis testing\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D\GitRepos\StatisticsBAandDS\DataScienceBootcamp\resources\Part_3_Statistics\S21_L136\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13308" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13305" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Dataset" sheetId="2" r:id="rId1"/>
@@ -22,13 +22,13 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Nonwhite!$B$4:$K$66</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">White!$B$4:$K$178</definedName>
   </definedNames>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="162913"/>
   <fileRecoveryPr autoRecover="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2488" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2489" uniqueCount="390">
   <si>
     <t>Age</t>
   </si>
@@ -1195,16 +1195,19 @@
   </si>
   <si>
     <t>Using the same methodology as in the lecture, find if there is pay gap based on race.</t>
+  </si>
+  <si>
+    <t>There is no pay gap based on race. Ther result is insignificant.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="_(&quot;$&quot;\²* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="_(&quot;$&quot;\²* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="21" x14ac:knownFonts="1">
     <font>
@@ -1685,7 +1688,7 @@
   </borders>
   <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -1737,74 +1740,74 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="18" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="18" fillId="33" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="18" fillId="33" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="18" fillId="33" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="18" fillId="33" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="18" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="18" fillId="33" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="18" fillId="33" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="18" fillId="33" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="18" fillId="33" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="18" fillId="33" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="18" fillId="33" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="18" fillId="33" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="18" fillId="33" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="18" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="43">
-    <cellStyle name="20% - Accent1" xfId="20" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="24" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="28" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="32" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="36" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="40" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="21" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="25" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="29" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="33" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="37" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="41" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="22" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="26" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="30" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="34" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="38" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="42" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="19" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="23" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="27" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="31" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="35" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="39" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="8" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="12" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="14" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Currency" xfId="1" builtinId="4"/>
-    <cellStyle name="Explanatory Text" xfId="17" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="7" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="3" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="4" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="5" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="6" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Input" xfId="10" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="13" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis1" xfId="20" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis2" xfId="24" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis3" xfId="28" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis4" xfId="32" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis5" xfId="36" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis6" xfId="40" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis1" xfId="21" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis2" xfId="25" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis3" xfId="29" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis4" xfId="33" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis5" xfId="37" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis6" xfId="41" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis1" xfId="22" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis2" xfId="26" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis3" xfId="30" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis4" xfId="34" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis5" xfId="38" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis6" xfId="42" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Bueno" xfId="7" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Cálculo" xfId="12" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Celda de comprobación" xfId="14" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Celda vinculada" xfId="13" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Encabezado 1" xfId="3" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Encabezado 4" xfId="6" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Énfasis1" xfId="19" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Énfasis2" xfId="23" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Énfasis3" xfId="27" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Énfasis4" xfId="31" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Énfasis5" xfId="35" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Énfasis6" xfId="39" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Entrada" xfId="10" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Incorrecto" xfId="8" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Neutral" xfId="9" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="16" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="11" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="2" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Notas" xfId="16" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Salida" xfId="11" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Texto de advertencia" xfId="15" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Texto explicativo" xfId="17" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Título" xfId="2" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Título 2" xfId="4" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Título 3" xfId="5" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Total" xfId="18" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="15" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2115,38 +2118,38 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L178"/>
-  <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="3.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.88671875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="19.5546875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="0" style="1" hidden="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.88671875" style="1"/>
+    <col min="2" max="2" width="12.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.7109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.85546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="19.5703125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="1.140625" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="1:12" ht="12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B2" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C2" s="4"/>
     </row>
-    <row r="4" spans="1:12" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
       <c r="B4" s="8" t="s">
         <v>223</v>
@@ -8453,38 +8456,38 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95E38930-1B40-454C-A087-8B026472BC0C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L178"/>
-  <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="3.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.88671875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="19.5546875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="0" style="1" hidden="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.88671875" style="1"/>
+    <col min="2" max="2" width="12.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.85546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="19.5703125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="0.85546875" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="1:12" ht="12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B2" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C2" s="4"/>
     </row>
-    <row r="4" spans="1:12" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
       <c r="B4" s="8" t="s">
         <v>223</v>
@@ -13052,38 +13055,38 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34BCEC06-AA75-436A-A5F7-40CC42DE6035}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L66"/>
-  <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="3.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.88671875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="19.5546875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.85546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="19.5703125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.7109375" style="1" customWidth="1"/>
     <col min="12" max="12" width="0" style="1" hidden="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.88671875" style="1"/>
+    <col min="13" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="1:12" ht="12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B2" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C2" s="4"/>
     </row>
-    <row r="4" spans="1:12" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
       <c r="B4" s="8" t="s">
         <v>223</v>
@@ -15355,34 +15358,34 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:K20"/>
-  <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="3.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="8.88671875" style="1"/>
-    <col min="11" max="11" width="8.88671875" style="10"/>
-    <col min="12" max="16384" width="8.88671875" style="1"/>
+    <col min="2" max="2" width="10.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="4" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="8.85546875" style="1"/>
+    <col min="11" max="11" width="8.85546875" style="10"/>
+    <col min="12" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="2:11" ht="12" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B2" s="4" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="4" spans="2:11" ht="12" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B4" s="4" t="s">
         <v>384</v>
       </c>
@@ -15398,7 +15401,7 @@
       <c r="E5" s="10"/>
       <c r="F5" s="10"/>
     </row>
-    <row r="6" spans="2:11" ht="12" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B6" s="4" t="s">
         <v>385</v>
       </c>
@@ -15409,21 +15412,21 @@
       <c r="E6" s="10"/>
       <c r="F6" s="10"/>
     </row>
-    <row r="7" spans="2:11" ht="12" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B7" s="22"/>
       <c r="C7" s="10"/>
       <c r="D7" s="18"/>
       <c r="E7" s="19"/>
       <c r="F7" s="10"/>
     </row>
-    <row r="8" spans="2:11" ht="12" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="4"/>
       <c r="C8" s="10"/>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
       <c r="F8" s="10"/>
     </row>
-    <row r="10" spans="2:11" ht="12" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="7" t="s">
         <v>379</v>
       </c>
@@ -15445,24 +15448,58 @@
       <c r="H10" s="7" t="s">
         <v>383</v>
       </c>
+      <c r="J10" s="1" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="14"/>
+      <c r="C11" s="1">
+        <f>COUNT(White!K5:K116)</f>
+        <v>112</v>
+      </c>
+      <c r="D11" s="9">
+        <f>AVERAGE(White!K5:K116)</f>
+        <v>67323.100000000006</v>
+      </c>
+      <c r="E11" s="15">
+        <f>_xlfn.VAR.S(White!K5:K116)</f>
+        <v>1136728018.0252261</v>
+      </c>
+      <c r="F11" s="15">
+        <f>((C11-1)*E11+(C12-1)*E12)/(C11+C12-2)</f>
+        <v>1168051481.9473374</v>
+      </c>
+      <c r="G11" s="14">
+        <f>(D11-D12)/F12</f>
+        <v>-0.66435038620328624</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0.51013200000000003</v>
+      </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B12" s="11" t="s">
         <v>380</v>
       </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="12"/>
+      <c r="C12" s="12">
+        <f>COUNT(Nonwhite!K5:K66)</f>
+        <v>62</v>
+      </c>
+      <c r="D12" s="13">
+        <f>AVERAGE(Nonwhite!K5:K66)</f>
+        <v>70917.264516129042</v>
+      </c>
+      <c r="E12" s="16">
+        <f>_xlfn.VAR.S(Nonwhite!K5:K66)</f>
+        <v>1225049916.2974083</v>
+      </c>
+      <c r="F12" s="12">
+        <f>SQRT((F11/C11)+(F11/C12))</f>
+        <v>5410.0435414351496</v>
+      </c>
       <c r="G12" s="12"/>
       <c r="H12" s="12"/>
     </row>
@@ -15475,7 +15512,7 @@
       <c r="G15" s="10"/>
       <c r="H15" s="10"/>
     </row>
-    <row r="16" spans="2:11" ht="12" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B16" s="17"/>
       <c r="C16" s="17"/>
       <c r="D16" s="17"/>
@@ -15502,7 +15539,7 @@
       <c r="G18" s="10"/>
       <c r="H18" s="10"/>
     </row>
-    <row r="19" spans="2:8" ht="12" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B19" s="22"/>
       <c r="C19" s="10"/>
       <c r="D19" s="18"/>
